--- a/research/traditional_assets/database/data/cyprus/cyprus_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_brokerage_investment_banking.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.355</v>
+        <v>-0.0549</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,97 +597,88 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-1.647058823529412</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="J2">
-        <v>-0.823529411764706</v>
+        <v>0.4298245614035088</v>
       </c>
       <c r="K2">
-        <v>-0.046</v>
+        <v>0.098</v>
       </c>
       <c r="L2">
-        <v>-0.9019607843137255</v>
+        <v>0.3223684210526316</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3364</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.5410526315789472</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>13.63673469387755</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.3364</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.5410526315789472</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>13.63673469387755</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>7.42</v>
+        <v>5.74</v>
       </c>
       <c r="V2">
-        <v>2.424836601307189</v>
+        <v>2.323886639676113</v>
       </c>
       <c r="W2">
-        <v>-0.009145129224652087</v>
+        <v>0.01888246628131021</v>
       </c>
       <c r="X2">
-        <v>0.04513361449802254</v>
+        <v>0.08663626531857743</v>
       </c>
       <c r="Y2">
-        <v>-0.05427874372267463</v>
-      </c>
-      <c r="Z2">
-        <v>-0.04003139717425432</v>
-      </c>
-      <c r="AA2">
-        <v>0.03296703296703297</v>
+        <v>-0.06775379903726722</v>
       </c>
       <c r="AB2">
-        <v>0.04508304692017478</v>
-      </c>
-      <c r="AC2">
-        <v>-0.01211601395314181</v>
+        <v>0.08632254438668244</v>
       </c>
       <c r="AD2">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AG2">
-        <v>-7.343</v>
+        <v>-5.672000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.02454574434172777</v>
+        <v>0.02679275019700552</v>
       </c>
       <c r="AI2">
-        <v>0.01461932789063983</v>
+        <v>0.02001177163037081</v>
       </c>
       <c r="AJ2">
-        <v>1.714452486574831</v>
+        <v>1.771392879450344</v>
       </c>
       <c r="AK2">
-        <v>3.410589874593591</v>
+        <v>2.421861656703672</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.051</v>
-      </c>
-      <c r="AQ2">
-        <v>1.647058823529412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +698,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.355</v>
+        <v>-0.0549</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -716,97 +707,88 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-1.647058823529412</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="J3">
-        <v>-0.823529411764706</v>
+        <v>0.4298245614035088</v>
       </c>
       <c r="K3">
-        <v>-0.046</v>
+        <v>0.098</v>
       </c>
       <c r="L3">
-        <v>-0.9019607843137255</v>
+        <v>0.3223684210526316</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.3364</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.5410526315789472</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>13.63673469387755</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.3364</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.5410526315789472</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>13.63673469387755</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>7.42</v>
+        <v>5.74</v>
       </c>
       <c r="V3">
-        <v>2.424836601307189</v>
+        <v>2.323886639676113</v>
       </c>
       <c r="W3">
-        <v>-0.009145129224652087</v>
+        <v>0.01888246628131021</v>
       </c>
       <c r="X3">
-        <v>0.04513361449802254</v>
+        <v>0.08663626531857743</v>
       </c>
       <c r="Y3">
-        <v>-0.05427874372267463</v>
-      </c>
-      <c r="Z3">
-        <v>-0.04003139717425432</v>
-      </c>
-      <c r="AA3">
-        <v>0.03296703296703297</v>
+        <v>-0.06775379903726722</v>
       </c>
       <c r="AB3">
-        <v>0.04508304692017478</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01211601395314181</v>
+        <v>0.08632254438668244</v>
       </c>
       <c r="AD3">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AG3">
-        <v>-7.343</v>
+        <v>-5.672000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.02454574434172777</v>
+        <v>0.02679275019700552</v>
       </c>
       <c r="AI3">
-        <v>0.01461932789063983</v>
+        <v>0.02001177163037081</v>
       </c>
       <c r="AJ3">
-        <v>1.714452486574831</v>
+        <v>1.771392879450344</v>
       </c>
       <c r="AK3">
-        <v>3.410589874593591</v>
+        <v>2.421861656703672</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.051</v>
-      </c>
-      <c r="AQ3">
-        <v>1.647058823529412</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cyprus/cyprus_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_brokerage_investment_banking.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0549</v>
+        <v>-0.363</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,34 +597,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.4473684210526316</v>
+        <v>-2.785714285714286</v>
       </c>
       <c r="J2">
-        <v>0.4298245614035088</v>
+        <v>-2.785714285714286</v>
       </c>
       <c r="K2">
-        <v>0.098</v>
+        <v>-0.119</v>
       </c>
       <c r="L2">
-        <v>0.3223684210526316</v>
+        <v>-4.25</v>
       </c>
       <c r="M2">
-        <v>1.3364</v>
+        <v>1.34</v>
       </c>
       <c r="N2">
-        <v>0.5410526315789472</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="O2">
-        <v>13.63673469387755</v>
+        <v>-11.26050420168067</v>
       </c>
       <c r="P2">
-        <v>1.3364</v>
+        <v>1.34</v>
       </c>
       <c r="Q2">
-        <v>0.5410526315789472</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="R2">
-        <v>13.63673469387755</v>
+        <v>-11.26050420168067</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,46 +633,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.74</v>
+        <v>6.02</v>
       </c>
       <c r="V2">
-        <v>2.323886639676113</v>
+        <v>2.487603305785124</v>
       </c>
       <c r="W2">
-        <v>0.01888246628131021</v>
+        <v>-0.03573573573573573</v>
       </c>
       <c r="X2">
-        <v>0.08663626531857743</v>
+        <v>0.06812268305648482</v>
       </c>
       <c r="Y2">
-        <v>-0.06775379903726722</v>
+        <v>-0.1038584187922205</v>
       </c>
       <c r="AB2">
-        <v>0.08632254438668244</v>
+        <v>0.06803321762267187</v>
       </c>
       <c r="AD2">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AG2">
-        <v>-5.672000000000001</v>
+        <v>-5.949</v>
       </c>
       <c r="AH2">
-        <v>0.02679275019700552</v>
+        <v>0.02850260939381774</v>
       </c>
       <c r="AI2">
-        <v>0.02001177163037081</v>
+        <v>0.02069367531331973</v>
       </c>
       <c r="AJ2">
-        <v>1.771392879450344</v>
+        <v>1.685746670444885</v>
       </c>
       <c r="AK2">
-        <v>2.421861656703672</v>
+        <v>2.297798377752028</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0549</v>
+        <v>-0.363</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -707,34 +707,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.4473684210526316</v>
+        <v>-2.785714285714286</v>
       </c>
       <c r="J3">
-        <v>0.4298245614035088</v>
+        <v>-2.785714285714286</v>
       </c>
       <c r="K3">
-        <v>0.098</v>
+        <v>-0.119</v>
       </c>
       <c r="L3">
-        <v>0.3223684210526316</v>
+        <v>-4.25</v>
       </c>
       <c r="M3">
-        <v>1.3364</v>
+        <v>1.34</v>
       </c>
       <c r="N3">
-        <v>0.5410526315789472</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="O3">
-        <v>13.63673469387755</v>
+        <v>-11.26050420168067</v>
       </c>
       <c r="P3">
-        <v>1.3364</v>
+        <v>1.34</v>
       </c>
       <c r="Q3">
-        <v>0.5410526315789472</v>
+        <v>0.5537190082644629</v>
       </c>
       <c r="R3">
-        <v>13.63673469387755</v>
+        <v>-11.26050420168067</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -743,46 +743,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.74</v>
+        <v>6.02</v>
       </c>
       <c r="V3">
-        <v>2.323886639676113</v>
+        <v>2.487603305785124</v>
       </c>
       <c r="W3">
-        <v>0.01888246628131021</v>
+        <v>-0.03573573573573573</v>
       </c>
       <c r="X3">
-        <v>0.08663626531857743</v>
+        <v>0.06812268305648482</v>
       </c>
       <c r="Y3">
-        <v>-0.06775379903726722</v>
+        <v>-0.1038584187922205</v>
       </c>
       <c r="AB3">
-        <v>0.08632254438668244</v>
+        <v>0.06803321762267187</v>
       </c>
       <c r="AD3">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AG3">
-        <v>-5.672000000000001</v>
+        <v>-5.949</v>
       </c>
       <c r="AH3">
-        <v>0.02679275019700552</v>
+        <v>0.02850260939381774</v>
       </c>
       <c r="AI3">
-        <v>0.02001177163037081</v>
+        <v>0.02069367531331973</v>
       </c>
       <c r="AJ3">
-        <v>1.771392879450344</v>
+        <v>1.685746670444885</v>
       </c>
       <c r="AK3">
-        <v>2.421861656703672</v>
+        <v>2.297798377752028</v>
       </c>
       <c r="AL3">
         <v>0</v>
